--- a/public/exports-from-60/69116418.xlsx
+++ b/public/exports-from-60/69116418.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166039</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166039</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166039</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166039</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183354</t>
+          <t xml:space="preserve">311183359</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183354</t>
+          <t xml:space="preserve">311183359</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183354</t>
+          <t xml:space="preserve">311183402</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -13879,12 +13879,12 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14029,12 +14029,12 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14104,12 +14104,12 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204999</t>
+          <t xml:space="preserve">311205022</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">

--- a/public/exports-from-60/69116418.xlsx
+++ b/public/exports-from-60/69116418.xlsx
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Voldgade 19A</t>
+          <t xml:space="preserve">Thygesminde Allé 1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8635786</t>
+          <t xml:space="preserve">100046399</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,21 +5985,21 @@
         </is>
       </c>
       <c r="J80">
-        <v>594</v>
+        <v>1047</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">100246391</t>
+          <t xml:space="preserve">200061734</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-25</t>
+          <t xml:space="preserve">2022-09-06</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thygesminde Allé 1</t>
+          <t xml:space="preserve">Vesterballevej 5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046399</t>
+          <t xml:space="preserve">9560002</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,21 +6060,21 @@
         </is>
       </c>
       <c r="J81">
-        <v>1047</v>
+        <v>2980</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">200061734</t>
+          <t xml:space="preserve">310027405</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-09-06</t>
+          <t xml:space="preserve">2023-02-28</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterballevej 5</t>
+          <t xml:space="preserve">Thygesminde Allé 3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,30 +6126,30 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560002</t>
+          <t xml:space="preserve">100046399</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J82">
-        <v>2980</v>
+        <v>3488</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">310027405</t>
+          <t xml:space="preserve">310035305</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Kuben Management A/S</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-28</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thygesminde Allé 3</t>
+          <t xml:space="preserve">Hannerup Brovej 9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,30 +6201,30 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046399</t>
+          <t xml:space="preserve">738033, 5670622</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>3488</v>
+        <v>561</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">310035305</t>
+          <t xml:space="preserve">311010183</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuben Management A/S</t>
+          <t xml:space="preserve">Vh-consult</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-16</t>
+          <t xml:space="preserve">2023-07-28</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hannerup Brovej 9</t>
+          <t xml:space="preserve">Kaalundsvej 1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">738033, 5670622</t>
+          <t xml:space="preserve">5665816</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="J84">
-        <v>561</v>
+        <v>170</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311010183</t>
+          <t xml:space="preserve">311033281</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vh-consult</t>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-28</t>
+          <t xml:space="preserve">2024-01-10</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaalundsvej 1</t>
+          <t xml:space="preserve">Tingskovvej 13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665816</t>
+          <t xml:space="preserve">4396084</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,21 +6360,21 @@
         </is>
       </c>
       <c r="J85">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311033281</t>
+          <t xml:space="preserve">311067367</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-10</t>
+          <t xml:space="preserve">2024-08-06</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingskovvej 13</t>
+          <t xml:space="preserve">Havepladsvej 177A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,30 +6426,30 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4396084</t>
+          <t xml:space="preserve">5666167</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J86">
-        <v>108</v>
+        <v>1413</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067367</t>
+          <t xml:space="preserve">311147951</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NiH Energy ApS</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-06</t>
+          <t xml:space="preserve">2025-11-30</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havepladsvej 177A</t>
+          <t xml:space="preserve">Chr. Winthers Vej 44</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,30 +6501,30 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666167</t>
+          <t xml:space="preserve">5668856</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J87">
-        <v>1413</v>
+        <v>2508</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147951</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NiH Energy ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-30</t>
+          <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chr. Winthers Vej 44</t>
+          <t xml:space="preserve">Skjoldborgsvej 25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J88">
-        <v>2508</v>
+        <v>1081</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J89">
-        <v>1081</v>
+        <v>416</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6731,11 +6731,11 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J90">
-        <v>416</v>
+        <v>705</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjoldborgsvej 25</t>
+          <t xml:space="preserve">Lollandsgade 2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,30 +6801,30 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5668856</t>
+          <t xml:space="preserve">5664903</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J91">
-        <v>705</v>
+        <v>2050</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311172659</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-21</t>
+          <t xml:space="preserve">2026-04-26</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lollandsgade 2</t>
+          <t xml:space="preserve">Sjællandsgade 23A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664903</t>
+          <t xml:space="preserve">5663527</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J92">
-        <v>2050</v>
+        <v>1598</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311172659</t>
+          <t xml:space="preserve">311173333</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-26</t>
+          <t xml:space="preserve">2026-04-28</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsgade 23A</t>
+          <t xml:space="preserve">Vejlevej 14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5663527</t>
+          <t xml:space="preserve">5673192</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="J93">
-        <v>1598</v>
+        <v>1257</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311173333</t>
+          <t xml:space="preserve">311173332</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlevej 14</t>
+          <t xml:space="preserve">Bragesvej 7</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5673192</t>
+          <t xml:space="preserve">5667534</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,11 +7035,11 @@
         </is>
       </c>
       <c r="J94">
-        <v>1257</v>
+        <v>755</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311173332</t>
+          <t xml:space="preserve">311176387</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-28</t>
+          <t xml:space="preserve">2026-05-13</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bragesvej 7</t>
+          <t xml:space="preserve">Bredstrupvej 41</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5667534</t>
+          <t xml:space="preserve">8506783</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,11 +7110,11 @@
         </is>
       </c>
       <c r="J95">
-        <v>755</v>
+        <v>976</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176387</t>
+          <t xml:space="preserve">311176386</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredstrupvej 41</t>
+          <t xml:space="preserve">Vendersgade 48</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8506783</t>
+          <t xml:space="preserve">5663424</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7185,11 +7185,11 @@
         </is>
       </c>
       <c r="J96">
-        <v>976</v>
+        <v>509</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176386</t>
+          <t xml:space="preserve">311349007</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 48</t>
+          <t xml:space="preserve">Bissensvej 1A</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5663424</t>
+          <t xml:space="preserve">5671656</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7260,11 +7260,11 @@
         </is>
       </c>
       <c r="J97">
-        <v>509</v>
+        <v>396</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349007</t>
+          <t xml:space="preserve">311176903</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-13</t>
+          <t xml:space="preserve">2026-05-17</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bissensvej 1A</t>
+          <t xml:space="preserve">Højmosevej 7</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671656</t>
+          <t xml:space="preserve">4394661</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176903</t>
+          <t xml:space="preserve">311176904</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmosevej 7</t>
+          <t xml:space="preserve">Mosegårdsvej 7A</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,20 +7401,20 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4394661</t>
+          <t xml:space="preserve">4395005</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J99">
-        <v>545</v>
+        <v>325</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176904</t>
+          <t xml:space="preserve">311176902</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 7A</t>
+          <t xml:space="preserve">Mosegårdsvej 7F</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J100">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 7F</t>
+          <t xml:space="preserve">Mosegårdsvej 7L</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J101">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 7L</t>
+          <t xml:space="preserve">Mosegårdsvej 7Q</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J102">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 7Q</t>
+          <t xml:space="preserve">Tingvejen 22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,20 +7701,20 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4395005</t>
+          <t xml:space="preserve">100009904</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>325</v>
+        <v>1450</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176902</t>
+          <t xml:space="preserve">311176899</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 22</t>
+          <t xml:space="preserve">Ullerupdalvej 233</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">100009904</t>
+          <t xml:space="preserve">5671590</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>1450</v>
+        <v>362</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176899</t>
+          <t xml:space="preserve">311177404</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-17</t>
+          <t xml:space="preserve">2026-05-19</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerupdalvej 233</t>
+          <t xml:space="preserve">Øster Voldgade 3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671590</t>
+          <t xml:space="preserve">5665369</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>362</v>
+        <v>1571</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177404</t>
+          <t xml:space="preserve">311179613</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-19</t>
+          <t xml:space="preserve">2026-05-30</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Voldgade 3</t>
+          <t xml:space="preserve">Damvej 1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665369</t>
+          <t xml:space="preserve">5669794</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>1571</v>
+        <v>634</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179613</t>
+          <t xml:space="preserve">311179816</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-30</t>
+          <t xml:space="preserve">2026-05-31</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 1</t>
+          <t xml:space="preserve">Havepladsvej 173</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,20 +8001,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5669794</t>
+          <t xml:space="preserve">5666167</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J107">
-        <v>634</v>
+        <v>168</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179816</t>
+          <t xml:space="preserve">311179818</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havepladsvej 173</t>
+          <t xml:space="preserve">Havepladsvej 175</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8081,11 +8081,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>168</v>
+        <v>6463</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havepladsvej 175</t>
+          <t xml:space="preserve">Havepladsvej 177</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8156,11 +8156,11 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J109">
-        <v>6463</v>
+        <v>385</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havepladsvej 177</t>
+          <t xml:space="preserve">Taulov Kirkevej 35A</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,20 +8226,20 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666167</t>
+          <t xml:space="preserve">7077980</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J110">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179818</t>
+          <t xml:space="preserve">311180015</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8306,11 +8306,11 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J111">
-        <v>350</v>
+        <v>579</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8381,11 +8381,11 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J112">
-        <v>579</v>
+        <v>967</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8456,11 +8456,11 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J113">
-        <v>967</v>
+        <v>903</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J114">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J115">
-        <v>903</v>
+        <v>3257</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taulov Kirkevej 35A</t>
+          <t xml:space="preserve">Herfordparken 1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,20 +8676,20 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7077980</t>
+          <t xml:space="preserve">100040538</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>3257</v>
+        <v>12410</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311180015</t>
+          <t xml:space="preserve">311183512</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-31</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herfordparken 1</t>
+          <t xml:space="preserve">Højdedraget 1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040538</t>
+          <t xml:space="preserve">4398224</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>12410</v>
+        <v>1697</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183512</t>
+          <t xml:space="preserve">311183515</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højdedraget 1</t>
+          <t xml:space="preserve">Højdedraget 2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4398224</t>
+          <t xml:space="preserve">4398311</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,11 +8835,11 @@
         </is>
       </c>
       <c r="J118">
-        <v>1697</v>
+        <v>445</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183515</t>
+          <t xml:space="preserve">311183342</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højdedraget 2</t>
+          <t xml:space="preserve">Kongensgade 9A</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,20 +8901,20 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4398311</t>
+          <t xml:space="preserve">5664154</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J119">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183342</t>
+          <t xml:space="preserve">311183444</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongensgade 9A</t>
+          <t xml:space="preserve">Lyngsoddevej 5</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,20 +8976,20 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664154</t>
+          <t xml:space="preserve">4393805</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>438</v>
+        <v>705</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183444</t>
+          <t xml:space="preserve">311183505</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngsoddevej 5</t>
+          <t xml:space="preserve">Skolesvinget 3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4393805</t>
+          <t xml:space="preserve">4391810</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="J121">
-        <v>705</v>
+        <v>2500</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183505</t>
+          <t xml:space="preserve">311183359</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9131,11 +9131,11 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J122">
-        <v>2500</v>
+        <v>1546</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 3</t>
+          <t xml:space="preserve">Skolesvinget 7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9206,15 +9206,15 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J123">
-        <v>1546</v>
+        <v>324</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183359</t>
+          <t xml:space="preserve">311183402</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 7</t>
+          <t xml:space="preserve">Søndermarksvej 130</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,20 +9276,20 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4391810</t>
+          <t xml:space="preserve">7489049</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>324</v>
+        <v>1101</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183402</t>
+          <t xml:space="preserve">311183409</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndermarksvej 130</t>
+          <t xml:space="preserve">Anders Billes Vej 26</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489049</t>
+          <t xml:space="preserve">5669032</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>1101</v>
+        <v>266</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183409</t>
+          <t xml:space="preserve">311183604</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Billes Vej 26</t>
+          <t xml:space="preserve">Jupitervej 29</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5669032</t>
+          <t xml:space="preserve">5666595</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183604</t>
+          <t xml:space="preserve">311183598</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 29</t>
+          <t xml:space="preserve">Bøgeskovvej 37B</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666595</t>
+          <t xml:space="preserve">5673910</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J127">
-        <v>276</v>
+        <v>1759</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183598</t>
+          <t xml:space="preserve">311184758</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-16</t>
+          <t xml:space="preserve">2026-06-21</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9581,11 +9581,11 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J128">
-        <v>1759</v>
+        <v>866</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgeskovvej 37B</t>
+          <t xml:space="preserve">Jacob Hansens Vej 5A</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,20 +9651,20 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5673910</t>
+          <t xml:space="preserve">1805168</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>866</v>
+        <v>1032</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184758</t>
+          <t xml:space="preserve">311184719</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacob Hansens Vej 5A</t>
+          <t xml:space="preserve">Jeppe Aakjærs Vej 2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805168</t>
+          <t xml:space="preserve">5668776</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,11 +9735,11 @@
         </is>
       </c>
       <c r="J130">
-        <v>1032</v>
+        <v>342</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184719</t>
+          <t xml:space="preserve">311184747</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeppe Aakjærs Vej 2</t>
+          <t xml:space="preserve">Jupitervej 30A</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5668776</t>
+          <t xml:space="preserve">5666593</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184747</t>
+          <t xml:space="preserve">311190979</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-21</t>
+          <t xml:space="preserve">2026-07-20</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30A</t>
+          <t xml:space="preserve">Tingvejen 31</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666593</t>
+          <t xml:space="preserve">4397145</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>311</v>
+        <v>7774</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190979</t>
+          <t xml:space="preserve">311190960</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 31</t>
+          <t xml:space="preserve">Dronningensgade 66</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4397145</t>
+          <t xml:space="preserve">5664362</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>7774</v>
+        <v>456</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190960</t>
+          <t xml:space="preserve">311191251</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-20</t>
+          <t xml:space="preserve">2026-07-22</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10031,11 +10031,11 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J134">
-        <v>456</v>
+        <v>223</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 66</t>
+          <t xml:space="preserve">Egumvej 52</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664362</t>
+          <t xml:space="preserve">8012611</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J135">
-        <v>223</v>
+        <v>733</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191251</t>
+          <t xml:space="preserve">311191300</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egumvej 52</t>
+          <t xml:space="preserve">Jupitervej 30B</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,20 +10176,20 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8012611</t>
+          <t xml:space="preserve">5666593</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J136">
-        <v>733</v>
+        <v>386</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191300</t>
+          <t xml:space="preserve">311192450</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-22</t>
+          <t xml:space="preserve">2026-08-01</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30B</t>
+          <t xml:space="preserve">Jupitervej 30C</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10256,15 +10256,15 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J137">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192450</t>
+          <t xml:space="preserve">311192453</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30C</t>
+          <t xml:space="preserve">Jupitervej 30D</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10331,11 +10331,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J138">
-        <v>383</v>
+        <v>130</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30D</t>
+          <t xml:space="preserve">Jupitervej 30E</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10406,15 +10406,15 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J139">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192453</t>
+          <t xml:space="preserve">311192456</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30E</t>
+          <t xml:space="preserve">Jupitervej 30F</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J140">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30F</t>
+          <t xml:space="preserve">Jupitervej 30G</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J141">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30G</t>
+          <t xml:space="preserve">Jupitervej 30H</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J142">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30H</t>
+          <t xml:space="preserve">Nørre Allé 1A</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,20 +10701,20 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666593</t>
+          <t xml:space="preserve">5671168</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J143">
-        <v>159</v>
+        <v>882</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192456</t>
+          <t xml:space="preserve">311192396</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Allé 1A</t>
+          <t xml:space="preserve">Nørre Allé 3A</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>882</v>
+        <v>1007</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Allé 3A</t>
+          <t xml:space="preserve">Prangervej 2A</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671168</t>
+          <t xml:space="preserve">5665886</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>1007</v>
+        <v>190</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192396</t>
+          <t xml:space="preserve">311192399</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J146">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -11006,15 +11006,15 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J147">
-        <v>63</v>
+        <v>1708</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192399</t>
+          <t xml:space="preserve">311192422</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11081,15 +11081,15 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J148">
-        <v>1708</v>
+        <v>1079</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192422</t>
+          <t xml:space="preserve">311192419</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prangervej 2A</t>
+          <t xml:space="preserve">Erritsø Bygade 85A</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,20 +11151,20 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665886</t>
+          <t xml:space="preserve">324492, 324493, 324494</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J149">
-        <v>1079</v>
+        <v>4772</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192419</t>
+          <t xml:space="preserve">311192568</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-01</t>
+          <t xml:space="preserve">2026-08-02</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erritsø Bygade 85A</t>
+          <t xml:space="preserve">Gothersgade 20</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">324492, 324493, 324494</t>
+          <t xml:space="preserve">7308352</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>4772</v>
+        <v>11624</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192568</t>
+          <t xml:space="preserve">311192535</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gothersgade 20</t>
+          <t xml:space="preserve">Krogsagervej 30</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,20 +11301,20 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">7308352</t>
+          <t xml:space="preserve">4395059</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J151">
-        <v>11624</v>
+        <v>247</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192535</t>
+          <t xml:space="preserve">311192576</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11381,11 +11381,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J152">
-        <v>247</v>
+        <v>138</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogsagervej 30</t>
+          <t xml:space="preserve">Krogsagervej 30A</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11456,11 +11456,11 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>138</v>
+        <v>9936</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogsagervej 30A</t>
+          <t xml:space="preserve">Prinsessegade 29</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4395059</t>
+          <t xml:space="preserve">5664659</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="J154">
-        <v>9936</v>
+        <v>1404</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192576</t>
+          <t xml:space="preserve">311192540</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prinsessegade 29</t>
+          <t xml:space="preserve">Randalsvej 51</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664659</t>
+          <t xml:space="preserve">5671426</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>1404</v>
+        <v>686</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192540</t>
+          <t xml:space="preserve">311294175</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11681,11 +11681,11 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J156">
-        <v>686</v>
+        <v>216</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Randalsvej 51</t>
+          <t xml:space="preserve">Indre Ringvej 173A</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671426</t>
+          <t xml:space="preserve">5672317</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>216</v>
+        <v>1640</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294175</t>
+          <t xml:space="preserve">311193728</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-02</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indre Ringvej 173A</t>
+          <t xml:space="preserve">Indre Ringvej 175</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11831,11 +11831,11 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J158">
-        <v>1640</v>
+        <v>695</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -11906,11 +11906,11 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J159">
-        <v>695</v>
+        <v>358</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11981,11 +11981,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J160">
-        <v>358</v>
+        <v>3300</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12056,11 +12056,11 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J161">
-        <v>3300</v>
+        <v>499</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12131,11 +12131,11 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J162">
-        <v>499</v>
+        <v>3364</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indre Ringvej 175</t>
+          <t xml:space="preserve">Skansevej 51</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12206,11 +12206,11 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J163">
-        <v>3364</v>
+        <v>1676</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansevej 51</t>
+          <t xml:space="preserve">Prinsessegade 27</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5672317</t>
+          <t xml:space="preserve">5664658</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>1676</v>
+        <v>5773</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311193728</t>
+          <t xml:space="preserve">311194185</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prinsessegade 27</t>
+          <t xml:space="preserve">Vendersgade 49</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664658</t>
+          <t xml:space="preserve">5663493</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>5773</v>
+        <v>3590</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194185</t>
+          <t xml:space="preserve">311194928</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 49</t>
+          <t xml:space="preserve">Erritsø Bygade 85B</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5663493</t>
+          <t xml:space="preserve">324490, 324491</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>3590</v>
+        <v>1750</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194928</t>
+          <t xml:space="preserve">311199931</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-17</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erritsø Bygade 85B</t>
+          <t xml:space="preserve">Gl. Landevej 45</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">324490, 324491</t>
+          <t xml:space="preserve">4394923</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>1750</v>
+        <v>958</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199931</t>
+          <t xml:space="preserve">311199890</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 45</t>
+          <t xml:space="preserve">Højmosevej 11</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4394923</t>
+          <t xml:space="preserve">8730679</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J168">
-        <v>958</v>
+        <v>200</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199890</t>
+          <t xml:space="preserve">311199897</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmosevej 11</t>
+          <t xml:space="preserve">Købmagergade 40</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730679</t>
+          <t xml:space="preserve">1809125</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>200</v>
+        <v>2418</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199897</t>
+          <t xml:space="preserve">311199920</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Købmagergade 40</t>
+          <t xml:space="preserve">Vendersgade 4</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809125</t>
+          <t xml:space="preserve">100075274</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,11 +12735,11 @@
         </is>
       </c>
       <c r="J170">
-        <v>2418</v>
+        <v>5956</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199920</t>
+          <t xml:space="preserve">311199924</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 4</t>
+          <t xml:space="preserve">Vendersgade 43</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">100075274</t>
+          <t xml:space="preserve">327334, 327335</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12810,11 +12810,11 @@
         </is>
       </c>
       <c r="J171">
-        <v>5956</v>
+        <v>2436</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199924</t>
+          <t xml:space="preserve">311199903</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 43</t>
+          <t xml:space="preserve">Høgevej 5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">327334, 327335</t>
+          <t xml:space="preserve">5668622</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12885,11 +12885,11 @@
         </is>
       </c>
       <c r="J172">
-        <v>2436</v>
+        <v>6177</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199903</t>
+          <t xml:space="preserve">311200238</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12956,11 +12956,11 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J173">
-        <v>6177</v>
+        <v>607</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13031,11 +13031,11 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J174">
-        <v>607</v>
+        <v>505</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13106,11 +13106,11 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J175">
-        <v>505</v>
+        <v>605</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13181,11 +13181,11 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J176">
-        <v>605</v>
+        <v>198</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13256,11 +13256,11 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J177">
-        <v>198</v>
+        <v>859</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høgevej 5</t>
+          <t xml:space="preserve">Højmosevej 2</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,20 +13326,20 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5668622</t>
+          <t xml:space="preserve">8730679</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J178">
-        <v>859</v>
+        <v>4305</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200238</t>
+          <t xml:space="preserve">311200242</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmosevej 2</t>
+          <t xml:space="preserve">Norgesgade 46A</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730679</t>
+          <t xml:space="preserve">5665460</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,11 +13410,11 @@
         </is>
       </c>
       <c r="J179">
-        <v>4305</v>
+        <v>1912</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200242</t>
+          <t xml:space="preserve">311200227</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesgade 46A</t>
+          <t xml:space="preserve">Prangervej 7</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665460</t>
+          <t xml:space="preserve">5665118</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,11 +13485,11 @@
         </is>
       </c>
       <c r="J180">
-        <v>1912</v>
+        <v>1159</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200227</t>
+          <t xml:space="preserve">311200210</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13556,15 +13556,15 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J181">
-        <v>1159</v>
+        <v>1107</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200210</t>
+          <t xml:space="preserve">311200127</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13631,15 +13631,15 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J182">
-        <v>1107</v>
+        <v>648</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200127</t>
+          <t xml:space="preserve">311200129</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prangervej 7</t>
+          <t xml:space="preserve">Viaduktvej 9A</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,20 +13701,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665118</t>
+          <t xml:space="preserve">7429396</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J183">
-        <v>648</v>
+        <v>2343</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200129</t>
+          <t xml:space="preserve">311200122</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viaduktvej 9A</t>
+          <t xml:space="preserve">Industrivej 8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13776,20 +13776,20 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7429396</t>
+          <t xml:space="preserve">5671399</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J184">
-        <v>2343</v>
+        <v>395</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200122</t>
+          <t xml:space="preserve">311200731</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13856,11 +13856,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J185">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 8</t>
+          <t xml:space="preserve">Kongensgade 111</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,25 +13926,25 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671399</t>
+          <t xml:space="preserve">8566948</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>284</v>
+        <v>5566</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200731</t>
+          <t xml:space="preserve">311200752</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongensgade 111</t>
+          <t xml:space="preserve">Røde Banke 73</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8566948</t>
+          <t xml:space="preserve">4392814</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,16 +14010,16 @@
         </is>
       </c>
       <c r="J187">
-        <v>5566</v>
+        <v>424</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200752</t>
+          <t xml:space="preserve">311200762</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røde Banke 73</t>
+          <t xml:space="preserve">Nymarksvej 205</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,20 +14076,20 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4392814</t>
+          <t xml:space="preserve">5672560</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J188">
-        <v>424</v>
+        <v>128</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200762</t>
+          <t xml:space="preserve">311202168</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarksvej 205</t>
+          <t xml:space="preserve">Nymarksvej 207</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14156,15 +14156,15 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J189">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202168</t>
+          <t xml:space="preserve">311202172</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14179,12 +14179,12 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarksvej 207</t>
+          <t xml:space="preserve">Nymarksvej 209</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J190">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarksvej 209</t>
+          <t xml:space="preserve">Nymarksvej 211</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J191">
@@ -14329,12 +14329,12 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarksvej 211</t>
+          <t xml:space="preserve">Nymarksvej 213</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J192">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarksvej 213</t>
+          <t xml:space="preserve">Nymarksvej 215</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14456,15 +14456,15 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J193">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202172</t>
+          <t xml:space="preserve">311202163</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14479,12 +14479,12 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarksvej 215</t>
+          <t xml:space="preserve">Erritsø Bygade 15A</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5672560</t>
+          <t xml:space="preserve">4392366</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>177</v>
+        <v>2517</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202163</t>
+          <t xml:space="preserve">311202290</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,17 +14549,17 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erritsø Bygade 15A</t>
+          <t xml:space="preserve">Skjoldborgsvej 21</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4392366</t>
+          <t xml:space="preserve">5668856</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>2517</v>
+        <v>5092</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202290</t>
+          <t xml:space="preserve">311202296</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjoldborgsvej 21</t>
+          <t xml:space="preserve">Trelde Næsvej 300</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5668856</t>
+          <t xml:space="preserve">9712209</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>5092</v>
+        <v>347</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202296</t>
+          <t xml:space="preserve">311202310</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trelde Næsvej 300</t>
+          <t xml:space="preserve">Trelde Næsvej 315</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,15 +14756,15 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J197">
-        <v>347</v>
+        <v>101</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202310</t>
+          <t xml:space="preserve">311202317</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trelde Næsvej 315</t>
+          <t xml:space="preserve">Øster Voldgade 18</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,20 +14826,20 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">9712209</t>
+          <t xml:space="preserve">5664300</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J198">
-        <v>101</v>
+        <v>6219</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202317</t>
+          <t xml:space="preserve">311202427</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14906,11 +14906,11 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J199">
-        <v>6219</v>
+        <v>1170</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14929,12 +14929,12 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14981,11 +14981,11 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J200">
-        <v>1170</v>
+        <v>4140</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -15004,12 +15004,12 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15056,11 +15056,11 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J201">
-        <v>4140</v>
+        <v>775</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -15079,12 +15079,12 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15131,11 +15131,11 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J202">
-        <v>775</v>
+        <v>474</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -15154,12 +15154,12 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Voldgade 18</t>
+          <t xml:space="preserve">Øster Voldgade 18M</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15206,11 +15206,11 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J203">
-        <v>474</v>
+        <v>362</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15229,12 +15229,12 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Voldgade 18M</t>
+          <t xml:space="preserve">Øster Voldgade 18N</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15281,11 +15281,11 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J204">
-        <v>362</v>
+        <v>800</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -15304,12 +15304,12 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Voldgade 18N</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,20 +15351,20 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664300</t>
+          <t xml:space="preserve">4396768</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J205">
-        <v>800</v>
+        <v>196</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202427</t>
+          <t xml:space="preserve">311202863</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,17 +15374,17 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Frantz Hansens Allé 1B</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15426,20 +15426,20 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4396768</t>
+          <t xml:space="preserve">8730871</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J206">
-        <v>196</v>
+        <v>269</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202863</t>
+          <t xml:space="preserve">311203335</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,17 +15449,17 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantz Hansens Allé 1B</t>
+          <t xml:space="preserve">Vigøvej 2</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,20 +15501,20 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730871</t>
+          <t xml:space="preserve">4397347</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>269</v>
+        <v>650</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203335</t>
+          <t xml:space="preserve">311203339</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15529,12 +15529,12 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigøvej 2</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">4397347</t>
+          <t xml:space="preserve">4396768</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>650</v>
+        <v>2227</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203339</t>
+          <t xml:space="preserve">311203417</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,17 +15599,17 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Nørre Allé 5</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,20 +15651,20 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4396768</t>
+          <t xml:space="preserve">5671171</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J209">
-        <v>2227</v>
+        <v>118</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203417</t>
+          <t xml:space="preserve">311204999</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15731,11 +15731,11 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J210">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -15806,15 +15806,15 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J211">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204999</t>
+          <t xml:space="preserve">311205022</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Allé 5</t>
+          <t xml:space="preserve">Ullerupdalvej 10A</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15881,15 +15881,15 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J212">
-        <v>165</v>
+        <v>1187</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205022</t>
+          <t xml:space="preserve">311204999</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerupdalvej 10A</t>
+          <t xml:space="preserve">Vestre Ringvej 100</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,20 +15951,20 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671171</t>
+          <t xml:space="preserve">9936679</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J213">
-        <v>1187</v>
+        <v>12573</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204999</t>
+          <t xml:space="preserve">311206580</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16031,11 +16031,11 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J214">
-        <v>12573</v>
+        <v>5071</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -16106,11 +16106,11 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J215">
-        <v>5071</v>
+        <v>4464</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J216">
-        <v>4464</v>
+        <v>1375</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Ringvej 100</t>
+          <t xml:space="preserve">Nørre Allé 5</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,20 +16251,20 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9936679</t>
+          <t xml:space="preserve">5671171</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J217">
-        <v>1375</v>
+        <v>12418</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206580</t>
+          <t xml:space="preserve">311213911</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Allé 5</t>
+          <t xml:space="preserve">Dronningensgade 95</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,30 +16326,30 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671171</t>
+          <t xml:space="preserve">7260988</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J218">
-        <v>12418</v>
+        <v>302</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213911</t>
+          <t xml:space="preserve">311340255</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 95</t>
+          <t xml:space="preserve">Dronningensgade 97A</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16406,11 +16406,11 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J219">
-        <v>302</v>
+        <v>4611</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -16481,11 +16481,11 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J220">
-        <v>4611</v>
+        <v>10047</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -16556,11 +16556,11 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J221">
-        <v>10047</v>
+        <v>701</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 97A</t>
+          <t xml:space="preserve">Dronningensgade 97B</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,11 +16631,11 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J222">
-        <v>701</v>
+        <v>7973</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 97B</t>
+          <t xml:space="preserve">Dronningensgade 97E</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J223">
-        <v>7973</v>
+        <v>1083</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 97E</t>
+          <t xml:space="preserve">Dronningensgade 97F</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16781,11 +16781,11 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J224">
-        <v>1083</v>
+        <v>940</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 97F</t>
+          <t xml:space="preserve">Sjællandsgade 108</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16856,11 +16856,11 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J225">
-        <v>940</v>
+        <v>1042</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsgade 108</t>
+          <t xml:space="preserve">Martine Christoffersens Vej 47A</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,30 +16926,30 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260988</t>
+          <t xml:space="preserve">100010739</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J226">
-        <v>1042</v>
+        <v>129</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340255</t>
+          <t xml:space="preserve">311370303</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">EL:CON A/S</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-08</t>
+          <t xml:space="preserve">2029-04-10</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martine Christoffersens Vej 47A</t>
+          <t xml:space="preserve">Martine Christoffersens Vej 57B</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,7 +17001,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">100010739</t>
+          <t xml:space="preserve">100010748</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311370303</t>
+          <t xml:space="preserve">311370383</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martine Christoffersens Vej 57B</t>
+          <t xml:space="preserve">Tingvejen 20</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">100010748</t>
+          <t xml:space="preserve">100176780</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -17085,21 +17085,21 @@
         </is>
       </c>
       <c r="J228">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311370383</t>
+          <t xml:space="preserve">311484000</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">EL:CON A/S</t>
+          <t xml:space="preserve">Factum2 A/S</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-10</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 20</t>
+          <t xml:space="preserve">Industrivej 26</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">100176780</t>
+          <t xml:space="preserve">7120196</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,21 +17160,21 @@
         </is>
       </c>
       <c r="J229">
-        <v>89</v>
+        <v>1996</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484000</t>
+          <t xml:space="preserve">311512465</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factum2 A/S</t>
+          <t xml:space="preserve">BYGTEST ApS</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-04-15</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 26</t>
+          <t xml:space="preserve">Snaremosevej 67</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17226,20 +17226,20 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">7120196</t>
+          <t xml:space="preserve">4393162</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J230">
-        <v>1996</v>
+        <v>149</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311512465</t>
+          <t xml:space="preserve">311543787</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-15</t>
+          <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snaremosevej 67</t>
+          <t xml:space="preserve">Snaremosevej 69</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,20 +17301,20 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4393162</t>
+          <t xml:space="preserve">4394659</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J231">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543787</t>
+          <t xml:space="preserve">311543773</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snaremosevej 69</t>
+          <t xml:space="preserve">Vejle Landevej 37</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4394659</t>
+          <t xml:space="preserve">4396083</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,21 +17385,21 @@
         </is>
       </c>
       <c r="J232">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543773</t>
+          <t xml:space="preserve">311577209</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">BYGTEST ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-27</t>
+          <t xml:space="preserve">2032-02-07</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejle Landevej 37</t>
+          <t xml:space="preserve">Vestre Ringvej 101</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">4396083</t>
+          <t xml:space="preserve">1509827</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -17460,11 +17460,11 @@
         </is>
       </c>
       <c r="J233">
-        <v>144</v>
+        <v>30856</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577209</t>
+          <t xml:space="preserve">311731153</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-07</t>
+          <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17531,15 +17531,15 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J234">
-        <v>30856</v>
+        <v>3066</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731153</t>
+          <t xml:space="preserve">311731047</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Ringvej 101</t>
+          <t xml:space="preserve">Bredstrupvej 67</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17601,30 +17601,30 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1509827</t>
+          <t xml:space="preserve">9015721</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>3066</v>
+        <v>240</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731047</t>
+          <t xml:space="preserve">311785759</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-22</t>
+          <t xml:space="preserve">2034-09-18</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredstrupvej 67</t>
+          <t xml:space="preserve">Madsbyvej 6</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17676,30 +17676,30 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9015721</t>
+          <t xml:space="preserve">8730852</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J236">
-        <v>240</v>
+        <v>832</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311785759</t>
+          <t xml:space="preserve">311786875</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-18</t>
+          <t xml:space="preserve">2034-09-24</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17756,15 +17756,15 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J237">
-        <v>832</v>
+        <v>220</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786872</t>
+          <t xml:space="preserve">311786875</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17831,15 +17831,15 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J238">
-        <v>220</v>
+        <v>154</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786872</t>
+          <t xml:space="preserve">311786875</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17906,15 +17906,15 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J239">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786872</t>
+          <t xml:space="preserve">311786875</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17981,15 +17981,15 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J240">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786872</t>
+          <t xml:space="preserve">311786875</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madsbyvej 6</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,30 +18051,30 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730852</t>
+          <t xml:space="preserve">4396768</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J241">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786872</t>
+          <t xml:space="preserve">311843406</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-24</t>
+          <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Dannevirkevej 4</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18126,30 +18126,30 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4396768</t>
+          <t xml:space="preserve">5669665</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843406</t>
+          <t xml:space="preserve">311917287</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-07</t>
+          <t xml:space="preserve">2036-08-04</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannevirkevej 4</t>
+          <t xml:space="preserve">Vester Voldgade 19A</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">5669665</t>
+          <t xml:space="preserve">8635786</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -18210,11 +18210,11 @@
         </is>
       </c>
       <c r="J243">
-        <v>240</v>
+        <v>594</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311917287</t>
+          <t xml:space="preserve">311928459</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-04</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">

--- a/public/exports-from-60/69116418.xlsx
+++ b/public/exports-from-60/69116418.xlsx
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311166039</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311166039</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311166039</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311166039</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183359</t>
+          <t xml:space="preserve">311183354</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183359</t>
+          <t xml:space="preserve">311183354</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183402</t>
+          <t xml:space="preserve">311183354</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -15679,12 +15679,12 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15754,12 +15754,12 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205022</t>
+          <t xml:space="preserve">311204999</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15829,12 +15829,12 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15904,12 +15904,12 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15979,12 +15979,12 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16054,12 +16054,12 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16204,12 +16204,12 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
